--- a/reports/Debug-snowbowl-20251216/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Week Ending (Actual)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
+    <t>Snowbowl Uplift Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
         <v>46006</v>
       </c>
       <c r="C3" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -459,10 +459,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="C4" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,7 +476,7 @@
         <v>46007</v>
       </c>
       <c r="C5" s="2">
-        <v>574</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +487,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,7 +504,7 @@
         <v>46007</v>
       </c>
       <c r="C7" s="2">
-        <v>90</v>
+        <v>574</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,13 +515,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="C9" s="2">
-        <v>1389</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
@@ -543,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="C10" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +557,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C11" s="2">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C12" s="2">
-        <v>94</v>
+        <v>661</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,7 +588,7 @@
         <v>46007</v>
       </c>
       <c r="C13" s="2">
-        <v>77</v>
+        <v>1416</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -599,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +616,10 @@
         <v>46006</v>
       </c>
       <c r="C15" s="2">
-        <v>71</v>
+        <v>1389</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +630,10 @@
         <v>46006</v>
       </c>
       <c r="C16" s="2">
-        <v>661</v>
+        <v>91</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>46007</v>
       </c>
       <c r="C17" s="2">
-        <v>1416</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
